--- a/simulacaoes_/custo_robustez_C13/_lote_resumo.xlsx
+++ b/simulacaoes_/custo_robustez_C13/_lote_resumo.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,67 +417,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>n_solucoes</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>volume_min</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>volume_max</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>hv_final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>gen_estab</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>sobol_ok</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>t_nsga2_s</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>t_sobol_s</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>t_total_s</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>avisos</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>erro</t>
         </is>
@@ -510,26 +498,26 @@
         <v>50</v>
       </c>
       <c r="D2" t="n">
-        <v>4.799745923264973</v>
+        <v>4.799906754623025</v>
       </c>
       <c r="E2" t="n">
-        <v>13.06119391745348</v>
+        <v>13.06605625800315</v>
       </c>
       <c r="F2" t="n">
-        <v>1.025269093626041</v>
+        <v>1.027161777719057</v>
       </c>
       <c r="G2" t="n">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>8.190335599996615</v>
+        <v>2.761679899999763</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>8.403046899999026</v>
+        <v>3.247475800000302</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
@@ -549,26 +537,26 @@
         <v>50</v>
       </c>
       <c r="D3" t="n">
-        <v>4.810149990699219</v>
+        <v>4.977071486191043</v>
       </c>
       <c r="E3" t="n">
-        <v>13.02953950562582</v>
+        <v>13.13874190465617</v>
       </c>
       <c r="F3" t="n">
-        <v>1.030278733674949</v>
+        <v>1.017072222331899</v>
       </c>
       <c r="G3" t="n">
-        <v>131</v>
+        <v>60</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>20.52373229997465</v>
+        <v>5.902750599999763</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>20.69059939996805</v>
+        <v>6.268491499999982</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
@@ -588,26 +576,26 @@
         <v>50</v>
       </c>
       <c r="D4" t="n">
-        <v>4.82587120227698</v>
+        <v>5.089643102348361</v>
       </c>
       <c r="E4" t="n">
-        <v>13.00321773644441</v>
+        <v>13.21233608481927</v>
       </c>
       <c r="F4" t="n">
-        <v>1.009838095169294</v>
+        <v>1.019474242876409</v>
       </c>
       <c r="G4" t="n">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>20.58397569996305</v>
+        <v>6.778922200000125</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>20.80658050003694</v>
+        <v>7.305194500000198</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
@@ -627,26 +615,26 @@
         <v>50</v>
       </c>
       <c r="D5" t="n">
-        <v>4.823515298535791</v>
+        <v>5.422355232942998</v>
       </c>
       <c r="E5" t="n">
-        <v>12.90659098343598</v>
+        <v>13.34988348768848</v>
       </c>
       <c r="F5" t="n">
-        <v>1.022611758757732</v>
+        <v>1.013878053604765</v>
       </c>
       <c r="G5" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>20.81892360001802</v>
+        <v>6.058303799999976</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>20.98811829998158</v>
+        <v>6.4911689999999</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>

--- a/simulacaoes_/custo_robustez_C13/_lote_resumo.xlsx
+++ b/simulacaoes_/custo_robustez_C13/_lote_resumo.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,71 +425,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>n_solucoes</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volume_min</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>volume_max</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>hv_final</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>gen_estab</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>sobol_ok</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>t_nsga2_s</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>t_sobol_s</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>t_total_s</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>avisos</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>erro</t>
         </is>
@@ -498,26 +510,26 @@
         <v>50</v>
       </c>
       <c r="D2" t="n">
-        <v>4.799906754623025</v>
+        <v>4.799745923264973</v>
       </c>
       <c r="E2" t="n">
-        <v>13.06605625800315</v>
+        <v>13.06119391745348</v>
       </c>
       <c r="F2" t="n">
-        <v>1.027161777719057</v>
+        <v>1.025269093626041</v>
       </c>
       <c r="G2" t="n">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>2.761679899999763</v>
+        <v>1.412728100083768</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>3.247475800000302</v>
+        <v>1.612148000043817</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
@@ -525,7 +537,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>rho025</t>
+          <t>rho050</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -537,26 +549,26 @@
         <v>50</v>
       </c>
       <c r="D3" t="n">
-        <v>4.977071486191043</v>
+        <v>5.089737398174898</v>
       </c>
       <c r="E3" t="n">
-        <v>13.13874190465617</v>
+        <v>13.21230167454317</v>
       </c>
       <c r="F3" t="n">
-        <v>1.017072222331899</v>
+        <v>1.017388219165847</v>
       </c>
       <c r="G3" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>5.902750599999763</v>
+        <v>2.835125199984759</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>6.268491499999982</v>
+        <v>2.987243999959901</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
@@ -564,7 +576,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>rho050</t>
+          <t>rho100</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -576,26 +588,26 @@
         <v>50</v>
       </c>
       <c r="D4" t="n">
-        <v>5.089643102348361</v>
+        <v>5.413971686785674</v>
       </c>
       <c r="E4" t="n">
-        <v>13.21233608481927</v>
+        <v>13.35339699808166</v>
       </c>
       <c r="F4" t="n">
-        <v>1.019474242876409</v>
+        <v>1.018436537333916</v>
       </c>
       <c r="G4" t="n">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>6.778922200000125</v>
+        <v>2.82980960002169</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>7.305194500000198</v>
+        <v>2.991837800014764</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
@@ -603,7 +615,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>rho100</t>
+          <t>rho150</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -615,29 +627,68 @@
         <v>50</v>
       </c>
       <c r="D5" t="n">
-        <v>5.422355232942998</v>
+        <v>5.787501461115749</v>
       </c>
       <c r="E5" t="n">
-        <v>13.34988348768848</v>
+        <v>13.28232945562801</v>
       </c>
       <c r="F5" t="n">
-        <v>1.013878053604765</v>
+        <v>1.00265297812072</v>
       </c>
       <c r="G5" t="n">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>6.058303799999976</v>
+        <v>2.87835879996419</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>6.4911689999999</v>
+        <v>3.082500400021672</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>rho200</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>50</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6.090634014927824</v>
+      </c>
+      <c r="E6" t="n">
+        <v>13.06291998046386</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9871839610172006</v>
+      </c>
+      <c r="G6" t="n">
+        <v>49</v>
+      </c>
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.866004000068642</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>3.019679800025187</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
